--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486355_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486355_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9701</v>
+        <v>4.0993</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6949</v>
+        <v>1.6084</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2752</v>
+        <v>2.4909</v>
       </c>
       <c r="G2" t="n">
         <v>4.6157</v>
@@ -610,13 +610,13 @@
         <v>2.8276</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2982</v>
+        <v>-1.169</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4074</v>
+        <v>-0.4939</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8908</v>
+        <v>-0.6751</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0262</v>
+        <v>2.0806</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.265</v>
+        <v>0.1032</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2911</v>
+        <v>1.9774</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2342</v>
+        <v>1.3461</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6598000000000001</v>
+        <v>1.1772</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8941</v>
+        <v>0.1689</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5039</v>
+        <v>1.8037</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9741</v>
+        <v>2.1264</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.4702</v>
+        <v>-0.3227</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7381</v>
+        <v>-0.4576</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3143</v>
+        <v>-0.9493</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.4916</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8276</v>
+        <v>3.2626</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8683</v>
+        <v>-0.5275</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4062</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4622</v>
+        <v>-0.6117</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7395</v>
+        <v>0.1745</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7395</v>
+        <v>-0.2159</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0121</v>
+        <v>1.4126</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0347</v>
+        <v>-1.7553</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9774</v>
+        <v>3.1678</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3461</v>
+        <v>-0.2342</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1772</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1689</v>
+        <v>-0.8941</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8037</v>
+        <v>0.5039</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1264</v>
+        <v>1.9741</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3227</v>
+        <v>-1.4702</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4576</v>
+        <v>-0.7381</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9493</v>
+        <v>-1.3143</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4916</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2626</v>
+        <v>2.8276</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.596</v>
+        <v>0.2548</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0156</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6117</v>
+        <v>0.3389</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1745</v>
+        <v>0.7395</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2159</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4723</v>
+        <v>0.1004</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7485</v>
+        <v>0.4074</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2761</v>
+        <v>-0.3069</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2905</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8721</v>
+        <v>0.5002</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3758</v>
+        <v>1.0347</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5036</v>
+        <v>-0.5345</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5443</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4995</v>
+        <v>-0.1025</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.2531</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4173</v>
+        <v>-0.3557</v>
       </c>
       <c r="G6" t="n">
         <v>-1.751</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7484</v>
+        <v>-0.3515</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3425</v>
+        <v>-0.0072</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4059</v>
+        <v>-0.3443</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5893</v>
+        <v>-0.2771</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0138</v>
+        <v>0.545</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5755</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1643</v>
@@ -1000,13 +1000,13 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7725</v>
+        <v>-0.4602</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6165</v>
+        <v>-0.0577</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.156</v>
+        <v>-0.4026</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5579</v>
+        <v>-0.5916</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0461</v>
+        <v>-3.4188</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4882</v>
+        <v>2.8272</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0288</v>
@@ -1078,13 +1078,13 @@
         <v>3.2626</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.074</v>
+        <v>-1.1077</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4384</v>
+        <v>-0.8111</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.2965</v>
       </c>
       <c r="V8" t="n">
         <v>0.3698</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. POIRIER</t>
+          <t>S. PENO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6612</v>
+        <v>-2.1268</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1063</v>
+        <v>-1.8676</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7675</v>
+        <v>-0.2592</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3891</v>
+        <v>-1.7693</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5668</v>
+        <v>-1.3382</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1778</v>
+        <v>-0.4311</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2398</v>
+        <v>-1.5684</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.757</v>
+        <v>-0.6903</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5172</v>
+        <v>-0.8781</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1493</v>
+        <v>-0.2009</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8098</v>
+        <v>-0.6479</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6606</v>
+        <v>0.447</v>
       </c>
       <c r="P9" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5772</v>
+        <v>-0.575</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3461</v>
+        <v>-0.2992</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9233</v>
+        <v>-0.2758</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. PENO</t>
+          <t>D. POIRIER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3002</v>
+        <v>-2.1322</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9794</v>
+        <v>-0.2722</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3208</v>
+        <v>-1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7693</v>
+        <v>-1.3891</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3382</v>
+        <v>-2.5668</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4311</v>
+        <v>1.1778</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5684</v>
+        <v>-0.2398</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6903</v>
+        <v>-0.757</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8781</v>
+        <v>0.5172</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2009</v>
+        <v>-1.1493</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6479</v>
+        <v>-1.8098</v>
       </c>
       <c r="O10" t="n">
-        <v>0.447</v>
+        <v>0.6606</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7484</v>
+        <v>-1.0482</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.411</v>
+        <v>-0.0324</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3374</v>
+        <v>-1.0157</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7943</v>
+        <v>-2.5377</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.155</v>
+        <v>-3.6827</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3608</v>
+        <v>1.145</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8955</v>
@@ -1312,13 +1312,13 @@
         <v>2.6101</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1866</v>
+        <v>0.4431</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1899</v>
+        <v>0.2824</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3765</v>
+        <v>0.1607</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5204</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2618</v>
+        <v>-3.4234</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0108</v>
+        <v>-2.2033</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.251</v>
+        <v>-1.2202</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9817</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1475</v>
+        <v>-0.3091</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3869</v>
+        <v>0.4206</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.7297</v>
       </c>
       <c r="V12" t="n">
         <v>1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1835</v>
+        <v>-3.4984</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.9678</v>
+        <v>-10.2828</v>
       </c>
       <c r="F13" t="n">
-        <v>6.7845</v>
+        <v>6.7842</v>
       </c>
       <c r="G13" t="n">
         <v>-5.5426</v>
@@ -1441,7 +1441,7 @@
         <v>3.0799</v>
       </c>
       <c r="J13" t="n">
-        <v>1.412099999999999</v>
+        <v>1.412100000000001</v>
       </c>
       <c r="K13" t="n">
         <v>3.348199999999999</v>
@@ -1450,7 +1450,7 @@
         <v>-1.9362</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.954400000000001</v>
+        <v>-6.9544</v>
       </c>
       <c r="N13" t="n">
         <v>-11.9706</v>
@@ -1459,7 +1459,7 @@
         <v>5.0161</v>
       </c>
       <c r="P13" t="n">
-        <v>4.35</v>
+        <v>4.349999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.313</v>
@@ -1468,13 +1468,13 @@
         <v>20.663</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.0352</v>
+        <v>-4.350099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6488999999999998</v>
+        <v>0.0361999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.3862</v>
+        <v>-4.386299999999999</v>
       </c>
       <c r="V13" t="n">
         <v>2.0441</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6523</v>
+        <v>5.5359</v>
       </c>
       <c r="E14" t="n">
         <v>3.3637</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2886</v>
+        <v>2.1723</v>
       </c>
       <c r="G14" t="n">
         <v>3.0375</v>
@@ -1546,13 +1546,13 @@
         <v>2.3926</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4625</v>
+        <v>1.3462</v>
       </c>
       <c r="T14" t="n">
         <v>1.4252</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9627</v>
+        <v>-0.079</v>
       </c>
       <c r="V14" t="n">
         <v>0.9347</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7913</v>
+        <v>2.3681</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2785</v>
+        <v>0.3064</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5128</v>
+        <v>2.0618</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6917</v>
+        <v>0.4241</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8518</v>
+        <v>1.4752</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8399</v>
+        <v>-1.051</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1859</v>
+        <v>0.5678</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0711</v>
+        <v>1.5789</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1147</v>
+        <v>-1.0112</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5058</v>
+        <v>-0.1436</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2193</v>
+        <v>-0.1038</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7251</v>
+        <v>-0.0399</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.6101</v>
+        <v>1.7401</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5145</v>
+        <v>-0.3404</v>
       </c>
       <c r="T15" t="n">
-        <v>3.0523</v>
+        <v>-0.4566</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4622</v>
+        <v>0.1163</v>
       </c>
       <c r="V15" t="n">
+        <v>0.5443</v>
+      </c>
+      <c r="W15" t="n">
         <v>0.1952</v>
       </c>
-      <c r="W15" t="n">
-        <v>0.3904</v>
-      </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3778</v>
+        <v>2.0783</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6446</v>
+        <v>1.5578</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0224</v>
+        <v>0.5205</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8876</v>
+        <v>2.8044</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6063</v>
+        <v>3.3822</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7188</v>
+        <v>-0.5777</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0861</v>
+        <v>3.4796</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5946</v>
+        <v>3.7839</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.5084</v>
+        <v>-0.3044</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8014</v>
+        <v>-0.6751</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0118</v>
+        <v>-0.4018</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7897</v>
+        <v>-0.2733</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4712</v>
+        <v>0.3836</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4252</v>
+        <v>0.0156</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0459</v>
+        <v>0.368</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8934</v>
+        <v>0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.8934</v>
+        <v>1.3252</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9873</v>
+        <v>1.4274</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2524</v>
+        <v>-2.0916</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2397</v>
+        <v>3.519</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4241</v>
+        <v>1.8876</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4752</v>
+        <v>2.6063</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.051</v>
+        <v>-0.7188</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5678</v>
+        <v>1.0861</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5789</v>
+        <v>2.5946</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0112</v>
+        <v>-1.5084</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1436</v>
+        <v>0.8014</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1038</v>
+        <v>0.0118</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0399</v>
+        <v>0.7897</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7401</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7212</v>
+        <v>1.5207</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0154</v>
+        <v>0.9782</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7058</v>
+        <v>0.5425</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5443</v>
+        <v>-0.8934</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1952</v>
+        <v>-0.8934</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7496</v>
+        <v>0.6995</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5113</v>
+        <v>0.3996</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2383</v>
+        <v>0.2999</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9648</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4317</v>
+        <v>0.3815</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1971</v>
+        <v>0.0853</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2346</v>
+        <v>0.2962</v>
       </c>
       <c r="V18" t="n">
         <v>0.1952</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6704</v>
+        <v>0.6564</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6637</v>
+        <v>-1.7331</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0067</v>
+        <v>2.3895</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8044</v>
+        <v>1.6917</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3822</v>
+        <v>0.8518</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5777</v>
+        <v>0.8399</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4796</v>
+        <v>1.1859</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7839</v>
+        <v>1.0711</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3044</v>
+        <v>0.1147</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6751</v>
+        <v>0.5058</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4018</v>
+        <v>-0.2193</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2733</v>
+        <v>0.7251</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.305</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>-4.3501</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0242</v>
+        <v>1.3795</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8784</v>
+        <v>1.0407</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1458</v>
+        <v>0.3389</v>
       </c>
       <c r="V19" t="n">
         <v>0.1952</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3252</v>
+        <v>0.3904</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>O. SIQUIER COSTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7857</v>
+        <v>-0.7614</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4031</v>
+        <v>-0.5353</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6175</v>
+        <v>-0.2261</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.909</v>
+        <v>-1.3223</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.6093</v>
+        <v>-0.3437</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2996</v>
+        <v>-0.9785</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.1207</v>
+        <v>-0.6903</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.159</v>
+        <v>0.0547</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0382</v>
+        <v>-0.7451</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7882</v>
+        <v>-0.632</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4504</v>
+        <v>-0.3985</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3379</v>
+        <v>-0.2335</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>1.144</v>
+        <v>0.3434</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8051</v>
+        <v>0.155</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3389</v>
+        <v>0.1884</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. SIQUIER COSTA</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8924</v>
+        <v>-1.0194</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7588</v>
+        <v>-2.6267</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1336</v>
+        <v>1.6073</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3223</v>
+        <v>-2.909</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3437</v>
+        <v>-2.6093</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9785</v>
+        <v>-0.2996</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6903</v>
+        <v>-2.1207</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0547</v>
+        <v>-2.159</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7451</v>
+        <v>0.0382</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.632</v>
+        <v>-0.7882</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3985</v>
+        <v>-0.4504</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2335</v>
+        <v>-0.3379</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2123</v>
+        <v>0.9103</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.5816</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2808</v>
+        <v>0.3287</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7774</v>
+        <v>-2.4459</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.535</v>
+        <v>-4.8645</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7577</v>
+        <v>2.4186</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4569</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2981</v>
+        <v>0.0333</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8904</v>
+        <v>-0.2199</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5923</v>
+        <v>0.2532</v>
       </c>
       <c r="V22" t="n">
         <v>0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5898</v>
+        <v>-2.8654</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0076</v>
+        <v>-0.5605</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5822</v>
+        <v>-2.3048</v>
       </c>
       <c r="G23" t="n">
         <v>3.3502</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1575</v>
+        <v>0.5669</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3341</v>
+        <v>0.7811</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4916</v>
+        <v>-0.2142</v>
       </c>
       <c r="V23" t="n">
         <v>-3.9549</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.183399999999999</v>
+        <v>5.6735</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.7843</v>
+        <v>-6.784199999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>10.9679</v>
+        <v>12.458</v>
       </c>
       <c r="G24" t="n">
         <v>5.5425</v>
@@ -2299,7 +2299,7 @@
         <v>-3.0797</v>
       </c>
       <c r="J24" t="n">
-        <v>6.954700000000001</v>
+        <v>6.954699999999999</v>
       </c>
       <c r="K24" t="n">
         <v>11.9705</v>
@@ -2314,7 +2314,7 @@
         <v>-3.3483</v>
       </c>
       <c r="O24" t="n">
-        <v>1.936199999999999</v>
+        <v>1.9362</v>
       </c>
       <c r="P24" t="n">
         <v>-4.3501</v>
@@ -2326,13 +2326,13 @@
         <v>16.3131</v>
       </c>
       <c r="S24" t="n">
-        <v>5.035200000000001</v>
+        <v>6.524999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>4.3863</v>
+        <v>4.386200000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6488</v>
+        <v>2.139</v>
       </c>
       <c r="V24" t="n">
         <v>-2.0442</v>
